--- a/test/fixtures/headers-no-scan-order-number.xlsx
+++ b/test/fixtures/headers-no-scan-order-number.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t xml:space="preserve">Data Source</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t xml:space="preserve">855123456718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-10 08:19:00</t>
   </si>
 </sst>
 </file>
@@ -2132,6 +2135,71 @@
         <v>37</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s" s="1">
+        <v>114</v>
+      </c>
+      <c r="D29" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="F29" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="H29" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="I29" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="J29" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>0.5</v>
+      </c>
+      <c r="M29">
+        <v>0.5</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="Q29" t="s" s="1">
+        <v>112</v>
+      </c>
+      <c r="R29" t="s" s="1">
+        <v>113</v>
+      </c>
+      <c r="S29" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="X29" t="s" s="1">
+        <v>32</v>
+      </c>
+      <c r="Y29" t="s" s="1">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>